--- a/hand_coding_tyler/cpc_llm_training_labels_tyler.xlsx
+++ b/hand_coding_tyler/cpc_llm_training_labels_tyler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tylerjacobson/Documents/GitHub/nyc_court_case/hand_coding_tyler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C6A1CF-F8F3-4544-BA77-03D1D8E1D3E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6880483-95E1-7F4C-AF17-918C1A57DD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31140" yWindow="-1280" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31140" yWindow="-1280" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coding" sheetId="1" r:id="rId1"/>
@@ -4509,7 +4509,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4541,6 +4541,12 @@
         <fgColor rgb="FF5C6470"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4554,7 +4560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4585,6 +4591,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4898,7 +4907,9 @@
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="7" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="15" width="17" customWidth="1"/>
     <col min="16" max="17" width="23" customWidth="1"/>
     <col min="18" max="22" width="17" customWidth="1"/>
@@ -4930,10 +4941,10 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="12" t="s">
         <v>1474</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="12" t="s">
         <v>1475</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -21464,8 +21475,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F301" xr:uid="{535B85A8-A264-0348-8711-17D1D40F9E71}">
       <formula1>"0,1,unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G301 G2" xr:uid="{1488D304-535E-A84D-A698-994F0B7C6B53}">
-      <formula1>"pro_dev, anti_dev, mixed, none"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G301" xr:uid="{E083FE13-9A21-434C-9010-34B68A793A70}">
+      <formula1>"upzone, downzone, mixed, none"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
